--- a/docs/gtm/marketplace-arbitrage/financial-model.xlsx
+++ b/docs/gtm/marketplace-arbitrage/financial-model.xlsx
@@ -1340,7 +1340,7 @@
         <v>3500</v>
       </c>
       <c r="H5" t="n">
-        <v>26759.26</v>
+        <v>31481.48</v>
       </c>
     </row>
     <row r="6">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="n">
-        <v>112410.14</v>
+        <v>117132.36</v>
       </c>
     </row>
   </sheetData>
